--- a/output/pdf_financials_xlsx/BAY.xlsx
+++ b/output/pdf_financials_xlsx/BAY.xlsx
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.131444</v>
@@ -1258,13 +1258,13 @@
         <v>-0.725091</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.288461</v>
+        <v>-3.288461</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="17">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.131444</v>
@@ -1542,13 +1542,13 @@
         <v>-0.725091</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3.288461</v>
+        <v>-3.288461</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="21">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.131444</v>
@@ -1707,13 +1707,13 @@
         <v>-0.725091</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>3.288461</v>
+        <v>-3.288461</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="24">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.925633</v>
+        <v>-0.925633</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-2.62888</v>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>164.42305</v>
+        <v>-164.42305</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.131444</v>
@@ -1953,13 +1953,13 @@
         <v>-0.725091</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>3.288461</v>
+        <v>-3.288461</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="28">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.131444</v>
@@ -2063,13 +2063,13 @@
         <v>-0.6417580000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>3.371795</v>
+        <v>-3.205127</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="30">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2205,13 +2205,13 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6138,10 +6138,10 @@
         <v>-3.288461</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="100">
@@ -33292,10 +33292,10 @@
         </is>
       </c>
       <c r="S263" s="5" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="T263" s="5" t="n">
-        <v>1.317231</v>
+        <v>-1.317231</v>
       </c>
     </row>
     <row r="264">
@@ -34057,10 +34057,10 @@
         </is>
       </c>
       <c r="R271" s="5" t="n">
-        <v>3.288461</v>
+        <v>-3.288461</v>
       </c>
       <c r="S271" s="5" t="n">
-        <v>1.960192</v>
+        <v>-1.960192</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -43082,10 +43082,10 @@
         </is>
       </c>
       <c r="E367" s="5" t="n">
-        <v>0.027769</v>
+        <v>-0.027769</v>
       </c>
       <c r="F367" s="5" t="n">
-        <v>0.131444</v>
+        <v>-0.131444</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BAY.xlsx
+++ b/output/pdf_financials_xlsx/BAY.xlsx
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001313</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005217</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013059</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-1.7e-05</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>-0.131444</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.144652</v>
+        <v>-0.143339</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.124703</v>
@@ -1935,13 +1935,13 @@
         <v>-1.5082</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.793346</v>
+        <v>-0.788129</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.926123</v>
+        <v>-1.913064</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.925768</v>
+        <v>-0.925751</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.43503</v>
@@ -2030,7 +2030,7 @@
         <v>-0.131444</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.144652</v>
+        <v>-0.143339</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.124703</v>
@@ -2045,13 +2045,13 @@
         <v>-1.5082</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.793346</v>
+        <v>-0.788129</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.926123</v>
+        <v>-1.913064</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.925768</v>
+        <v>-0.925751</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.43503</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.119183</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.282054</v>
+        <v>0.412876</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.255109</v>
+        <v>0.015766</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.007746</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.048256</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.302937</v>
@@ -2359,10 +2359,10 @@
         <v>0.552894</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.426275</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.08529399999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2429,19 +2429,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.119183</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.282054</v>
+        <v>0.412876</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.255109</v>
+        <v>0.015766</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.007746</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.048256</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.302937</v>
@@ -2473,10 +2473,10 @@
         <v>0.552894</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.426275</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.08529399999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.119183</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.155822</v>
+        <v>0.025</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.02313</v>
+        <v>0.015384</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.054161</v>
+        <v>0.005905</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.246697</v>
@@ -3157,10 +3157,10 @@
         <v>0.11234</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.512224</v>
+        <v>0.085949</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.293636</v>
+        <v>0.208342</v>
       </c>
     </row>
     <row r="49">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -36558,7 +36558,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -41644,7 +41644,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">

--- a/output/pdf_financials_xlsx/BAY.xlsx
+++ b/output/pdf_financials_xlsx/BAY.xlsx
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.1535</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.963706</v>
@@ -16340,7 +16340,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.1535</v>
       </c>
@@ -16530,7 +16534,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
